--- a/Health systems - FMOH Use Case Prioritization Criteria.xlsx
+++ b/Health systems - FMOH Use Case Prioritization Criteria.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Please suggest potential collaborators/institutions</t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH/HSIQ LEO</t>
+    <t xml:space="preserve">MoH/HSIQ LEO</t>
   </si>
   <si>
     <t xml:space="preserve">Health Systems</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">- Ethiopian health Insurance, SAEO,  EPHI, MoH HR; EPSS, International collaborators i.e. Imperial, Local academic instituitions; FENOT HARVARD University School of Public Health (working on evidence), World Bank, WHO</t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH/EBTBS</t>
+    <t xml:space="preserve">MoH/EBTBS</t>
   </si>
   <si>
     <t xml:space="preserve">Blood services - forecast demand and assess supply gaps to inform national planning</t>
@@ -105,10 +105,10 @@
     <t xml:space="preserve">- High relevance with key matrix due to PPH and maternal health; Decision support lower point because it also relies on demand from stakeholders which is more complicated; Data through the blood information system but data quality issues persist; It is an institutional priority and data mostly inhouse; </t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH, Regional Health Bureau, WHO, Local academic institions, Health facilities </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FMoH/Ethiopian blood and tissue and bank</t>
+    <t xml:space="preserve">MoH, Regional Health Bureau, WHO, Local academic institions, Health facilities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MoH/Ethiopian blood and tissue and bank</t>
   </si>
   <si>
     <t xml:space="preserve">Kidney services - estimate burden and forecast demand for transplant services</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">- Kidney Transplant Society; Patient Groups; Transplant profesionals society; MoH, Tertiary Health Facilities; </t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH/FDA</t>
+    <t xml:space="preserve">MoH/FDA</t>
   </si>
   <si>
     <t xml:space="preserve">Regulatory (food &amp; health products) - assess coverage and determine effectiveness of regulatory systems for safety outcomes</t>
@@ -142,16 +142,16 @@
     <t xml:space="preserve">- It is an instituitional priority for the orgnaisation; Inhouse data available for historical analysis and to inform modelling from the regulator's side but the consumer side is lacking; </t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH, EPSS, EPHI, Academia, WHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FMoH/Hawassa University</t>
+    <t xml:space="preserve">MoH, EPSS, EPHI, Academia, WHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MoH/Hawassa University</t>
   </si>
   <si>
     <t xml:space="preserve">NCDs and health inequalities - improve forecasting of NCD incidence and disease burden using routine and risk factor data</t>
   </si>
   <si>
-    <t xml:space="preserve">How can predictive models using routine health and risk factor data improve forecasting of NCD incidence and burden in Ethiopia for Health intelligence?</t>
+    <t xml:space="preserve">1. How can predictive models using routine health and risk factor data improve forecasting of NCD incidence and burden in Ethiopia for Health intelligence?</t>
   </si>
   <si>
     <t xml:space="preserve">- High relevance due to NCD importance in national plans; Good data availability from different sources including STEPS survey; There were questions as to the quality and depth of data even though different data sources exist</t>
@@ -160,7 +160,7 @@
     <t xml:space="preserve">- WHO, EPHI, MOH NCD team; CSA </t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH/Health System Innovation and Quality</t>
+    <t xml:space="preserve">MoH/Health System Innovation and Quality</t>
   </si>
   <si>
     <t xml:space="preserve">Health facility readiness - assess facility readiness and identify gaps affecting service delivery</t>
@@ -186,7 +186,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +245,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -307,7 +313,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -344,7 +350,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -353,6 +359,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -633,7 +643,7 @@
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
     </row>
-    <row r="2" customFormat="false" ht="267.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="255.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
@@ -741,7 +751,7 @@
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="280.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="267.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
         <v>25</v>
       </c>
@@ -859,7 +869,7 @@
       <c r="C6" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="12" t="s">
         <v>37</v>
       </c>
       <c r="E6" s="6" t="n">
@@ -913,7 +923,7 @@
       <c r="C7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="12" t="s">
         <v>42</v>
       </c>
       <c r="E7" s="6" t="n">
@@ -988,33 +998,33 @@
       <c r="Z9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
       <c r="D12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
       <c r="D13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
